--- a/ig/nr-add-svs-profile/StructureDefinition-as-practitioner.xlsx
+++ b/ig/nr-add-svs-profile/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-07T09:13:35+00:00</t>
+    <t>2024-02-07T12:54:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -745,7 +745,8 @@
 </t>
   </si>
   <si>
-    <t>Description of identifier</t>
+    <t>Type d’identifiant national de la personne physique (typeIdNat_PP),
+Les codes ADELI, RPPS et IDNPS proviennent du system  http://interopsante.org/fhir/CodeSystem/fr-v2-0203 ; Les codes 1, 3, 4, 5, 6 proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne</t>
   </si>
   <si>
     <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
@@ -1015,8 +1016,7 @@
     <t>Practitioner.identifier:idNatPs.type</t>
   </si>
   <si>
-    <t>Type d’identifiant national de la personne physique (typeIdNat_PP),
-Les codes ADELI, RPPS et IDNPS proviennent du system  http://interopsante.org/fhir/CodeSystem/fr-v2-0203 ; Les codes 1, 3, 4, 5, 6 proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne</t>
+    <t>Description of identifier</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -10869,7 +10869,7 @@
         <v>231</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>232</v>
+        <v>319</v>
       </c>
       <c r="M68" t="s" s="2">
         <v>233</v>
@@ -12923,7 +12923,7 @@
         <v>231</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>232</v>
+        <v>319</v>
       </c>
       <c r="M88" t="s" s="2">
         <v>233</v>
